--- a/output/2026年4月/2026年4月党费汇总表.xlsx
+++ b/output/2026年4月/2026年4月党费汇总表.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -516,14 +516,14 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>测试支部1</t>
+          <t>2026年计算机科学与技术学院本科生第一党支部</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>7.9</v>
+        <v>14</v>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
     </row>
@@ -533,14 +533,14 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>测试支部2</t>
+          <t>2026年计算机科学与技术学院本科生第二党支部</t>
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0</v>
+        <v>13.2</v>
       </c>
       <c r="E5" s="6" t="inlineStr"/>
     </row>
@@ -550,14 +550,14 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>本科生第一党支部</t>
+          <t>2026年计算机科学与技术学院本科生第三党支部</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>167.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" s="4" t="inlineStr"/>
     </row>
@@ -567,14 +567,14 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>所属党支部</t>
+          <t>2026年计算机科学与技术学院本科生第四党支部</t>
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E7" s="6" t="inlineStr"/>
     </row>
@@ -584,14 +584,14 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>中共新疆大学计算机科学与技术学院本科生第三支部委员会</t>
+          <t>2026年计算机科学与技术学院本科生第五党支部</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0</v>
+        <v>45.6</v>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
     </row>
@@ -601,14 +601,14 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>中共新疆大学计算机科学与技术学院本科生第四支部委员会</t>
+          <t>2026年计算机科学与技术学院本科生第六党支部</t>
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="E9" s="6" t="inlineStr"/>
     </row>
@@ -618,14 +618,14 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>中共新疆大学计算机科学与技术学院本科生第五支部委员会</t>
+          <t>2026年计算机科学与技术学院本科生第七党支部</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="E10" s="4" t="inlineStr"/>
     </row>
@@ -635,14 +635,14 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>中共新疆大学计算机科学与技术学院本科生第六支部委员会</t>
+          <t>2026年计算机科学与技术学院本科生第八党支部</t>
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0</v>
+        <v>31.2</v>
       </c>
       <c r="E11" s="6" t="inlineStr"/>
     </row>
@@ -652,14 +652,14 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>中共新疆大学计算机科学与技术学院本科生第七支部委员会</t>
+          <t>2026年计算机科学与技术学院本科生第九党支部</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E12" s="4" t="inlineStr"/>
     </row>
@@ -669,14 +669,14 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>中共新疆大学计算机科学与技术学院本科生第八支部委员会</t>
+          <t>2026年计算机科学与技术学院本科生第十党支部</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="E13" s="6" t="inlineStr"/>
     </row>
@@ -686,14 +686,14 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>中共新疆大学计算机科学与技术学院本科生第九支部委员会</t>
+          <t>2026年计算机科学与技术学院本科生第十一党支部</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
     </row>
@@ -703,14 +703,14 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>中共新疆大学计算机科学与技术学院本科生第十支部委员会</t>
+          <t>2026年计算机科学与技术学院本科生第十二党支部</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="E15" s="6" t="inlineStr"/>
     </row>
@@ -720,11 +720,11 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>中共新疆大学计算机科学与技术学院本科生第十一支部委员会</t>
+          <t>2026年计算机科学与技术学院研究生第一党支部</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>0</v>
@@ -737,11 +737,11 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>中共新疆大学计算机科学与技术学院本科生第十二支部委员会</t>
+          <t>2026年计算机科学与技术学院研究生第二党支部</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>0</v>
@@ -754,11 +754,11 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>中共新疆大学计算机科学与技术学院研究生第一支部委员会</t>
+          <t>2026年计算机科学与技术学院研究生第三党支部</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>0</v>
@@ -771,11 +771,11 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>中共新疆大学计算机科学与技术学院研究生第二支部委员会</t>
+          <t>2026年计算机科学与技术学院研究生第四党支部</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>0</v>
@@ -788,11 +788,11 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>中共新疆大学计算机科学与技术学院研究生第三支部委员会</t>
+          <t>2026年计算机科学与技术学院研究生第五党支部</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>0</v>
@@ -805,11 +805,11 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>中共新疆大学计算机科学与技术学院研究生第四支部委员会</t>
+          <t>2026年计算机科学与技术学院研究生第六党支部</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>0</v>
@@ -822,11 +822,11 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>中共新疆大学计算机科学与技术学院研究生第五支部委员会</t>
+          <t>2026年计算机科学与技术学院研究生第七党支部</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
@@ -839,11 +839,11 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>中共新疆大学计算机科学与技术学院研究生第六支部委员会</t>
+          <t>2026年计算机科学与技术学院研究生第八党支部</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>0</v>
@@ -856,11 +856,11 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>中共新疆大学计算机科学与技术学院研究生第七支部委员会</t>
+          <t>2026年计算机科学与技术学院研究生第九党支部</t>
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>0</v>
@@ -868,212 +868,25 @@
       <c r="E24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>中共新疆大学计算机科学与技术学院研究生第八支部委员会</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>中共新疆大学计算机科学与技术学院研究生第九支部委员会</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="4" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>2026年计算机科学与技术学院研究生第一党支部</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>38</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="6" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>2026年计算机科学与技术学院研究生第二党支部</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="4" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>2026年计算机科学与技术学院研究生第三党支部</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>2026年计算机科学与技术学院研究生第四党支部</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="4" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>2026年计算机科学与技术学院研究生第五党支部</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>48</v>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="6" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>2026年计算机科学与技术学院研究生第六党支部</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="n">
-        <v>28</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="4" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="n">
-        <v>30</v>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>2026年计算机科学与技术学院研究生第七党支部</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="6" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>2026年计算机科学与技术学院研究生第八党支部</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="4" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>2026年计算机科学与技术学院研究生第九党支部</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="6" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B36" s="7" t="n"/>
-      <c r="C36" s="2" t="n">
-        <v>838</v>
-      </c>
-      <c r="D36" s="2" t="n">
-        <v>175.3</v>
-      </c>
-      <c r="E36" s="8" t="inlineStr"/>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="2" t="n">
+        <v>509</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>249.5</v>
+      </c>
+      <c r="E25" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A25:B25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
